--- a/artfynd/A 22662-2026 artfynd.xlsx
+++ b/artfynd/A 22662-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,51 +680,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101461100</v>
+        <v>137283872</v>
       </c>
       <c r="B2" t="n">
-        <v>99792</v>
+        <v>58015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222315</v>
+        <v>100110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klapperstarr</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex glareosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Wahlenb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Umeå, Vb</t>
+          <t>Ljumviksudden, Holmsund, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>764937</v>
+        <v>764912</v>
       </c>
       <c r="R2" t="n">
-        <v>7073953</v>
+        <v>7074008</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,17 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fläckvis vanlig</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,32 +777,27 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Marin strandvåtmark</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Gardfjell</t>
+          <t>Christer  Nordeman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Gardfjell</t>
+          <t>Christer  Nordeman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101461100</t>
+          <t>https://artportalen.se/Sighting/137283872</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114325577</v>
+        <v>101461100</v>
       </c>
       <c r="B3" t="n">
         <v>99792</v>
@@ -832,13 +831,14 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Umeå, Ljumviken, Vb</t>
+          <t>Umeå, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764936</v>
+        <v>764937</v>
       </c>
       <c r="R3" t="n">
         <v>7073953</v>
@@ -866,11 +866,6 @@
           <t>Umeå socken</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>AC-Ume-0058</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2022-06-06</t>
@@ -895,23 +890,145 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Marin strandvåtmark</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Hans Gardfjell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hans Gardfjell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101461100</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114325577</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99792</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222315</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Klapperstarr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carex glareosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Wahlenb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Umeå, Ljumviken, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>764936</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7073953</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>AC-Ume-0058</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fläckvis vanlig</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Sofia Lund</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Hans Gardfjell</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/114325577</t>
         </is>
@@ -921,6 +1038,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22662-2026 artfynd.xlsx
+++ b/artfynd/A 22662-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283872</v>
       </c>
       <c r="B2" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22662-2026 artfynd.xlsx
+++ b/artfynd/A 22662-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283872</v>
       </c>
       <c r="B2" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22662-2026 artfynd.xlsx
+++ b/artfynd/A 22662-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283872</v>
       </c>
       <c r="B2" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22662-2026 artfynd.xlsx
+++ b/artfynd/A 22662-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283872</v>
       </c>
       <c r="B2" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
